--- a/AAII_Financials/Quarterly/RTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>RTX</t>
   </si>
@@ -656,431 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24708000</v>
+      </c>
+      <c r="E8" s="3">
         <v>22076000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24238000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22478000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21581000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20306000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21623000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20089000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19721000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19305000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19927000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13464000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18315000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17214000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18093000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16951000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16314000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15716000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17044000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16213000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15880000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>15251000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16419000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14747000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14061000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11360000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11694000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11373000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11329000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10953000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>18044000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>16510000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>16705000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>19575000</v>
+      </c>
+      <c r="E9" s="3">
         <v>17482000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19521000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17898000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17205000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16190000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17388000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16055000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16141000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15744000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16018000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12750000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14518000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13645000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14526000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13464000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12856000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12560000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13607000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13085000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12654000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12517000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14199000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12862000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12031000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15196000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12904000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>18933000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>19391000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>18649000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>13712000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12510000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>12375000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5133000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4594000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4717000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4580000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4376000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4116000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4235000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4034000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3580000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3561000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3909000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>714000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3797000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3569000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3567000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3487000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3458000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3156000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3437000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3128000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3226000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2734000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2220000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1885000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2030000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-3836000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-1210000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-7560000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-8062000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-7696000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4332000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4000000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4330000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1116,109 +1128,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>726000</v>
+      </c>
+      <c r="E12" s="3">
         <v>627000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>789000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>684000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>697000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>637000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>808000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>751000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>706000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>669000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>757000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>712000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>729000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>607000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>716000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>662000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>698000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>635000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>810000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>676000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>657000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>589000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>710000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>642000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>695000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>535000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>668000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>592000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>605000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>587000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>733000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>586000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>589000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1318,43 +1334,46 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="3">
         <v>-25000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-100000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="3">
         <v>-200000</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>918000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-415000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-200000</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>24</v>
@@ -1362,11 +1381,11 @@
       <c r="P14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>24</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>24</v>
@@ -1374,98 +1393,101 @@
       <c r="T14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" s="3">
         <v>674000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>19000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>56000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>43000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>92000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>250000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3610000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>668000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>181000</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>66000</v>
       </c>
       <c r="AE14" s="3">
         <v>66000</v>
       </c>
       <c r="AF14" s="3">
+        <v>66000</v>
+      </c>
+      <c r="AG14" s="3">
         <v>56000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>121000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>37000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1079000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1071000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1159000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1091000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1076000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1052000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1139000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1094000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1072000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>1059000</v>
       </c>
       <c r="M15" s="3">
         <v>1059000</v>
       </c>
       <c r="N15" s="3">
+        <v>1059000</v>
+      </c>
+      <c r="O15" s="3">
         <v>1074000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1044000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1034000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1520,8 +1542,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1554,210 +1579,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>21571000</v>
+      </c>
+      <c r="E17" s="3">
         <v>19166000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21566000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19691000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19089000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17905000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19328000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17687000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17906000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17464000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17795000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14414000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16353000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15083000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16602000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15431000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14961000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14636000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16373000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14870000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14598000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14238000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>16281000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>14318000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>17821000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10065000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10738000</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>9943000</v>
       </c>
       <c r="AE17" s="3">
         <v>9943000</v>
       </c>
       <c r="AF17" s="3">
+        <v>9943000</v>
+      </c>
+      <c r="AG17" s="3">
         <v>9811000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>16133000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>14672000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>13831000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3137000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2910000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2672000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2787000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2492000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2401000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2295000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2402000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1815000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1841000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2132000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-950000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1962000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2131000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1491000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1520000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1353000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1080000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>671000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1343000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1282000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1013000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>138000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>429000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3760000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1295000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>956000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1430000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1386000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1142000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1911000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1838000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2874000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1793,513 +1825,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="3">
         <v>8000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>12000</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7000</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100000</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>481000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>483000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>465000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>484000</v>
       </c>
       <c r="U20" s="3">
         <v>484000</v>
       </c>
       <c r="V20" s="3">
+        <v>484000</v>
+      </c>
+      <c r="W20" s="3">
         <v>500000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>494000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>502000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>266000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>264000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>248000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>175000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>167000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>311000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>268000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>203000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>265000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>253000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>218000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4216000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3973000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3828000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3866000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3568000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3461000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3435000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3503000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2887000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2904000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3091000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>124000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3006000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3179000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3020000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3050000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2817000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2578000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2299000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3001000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2908000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2638000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1557000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1857000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2401000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2198000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1809000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2433000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2042000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2287000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2843000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2684000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3684000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E22" s="3">
         <v>406000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>370000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>483000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>480000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>502000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>514000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>548000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>488000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>420000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>551000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>391000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>372000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>339000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>332000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>326000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>320000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>322000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>288000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>367000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>346000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>357000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>367000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>356000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>346000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>339000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>436000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>424000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>420000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>431000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>388000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>323000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>258000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>2742000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2520000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2297000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2438000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2040000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1958000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2009000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1906000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>428000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1851000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1735000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1322000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1607000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1816000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1640000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1677000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1498000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1242000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>867000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1476000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1430000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1158000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>37000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>337000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3858000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1131000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>687000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1317000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1234000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>914000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1788000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1768000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2834000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>493000</v>
+      </c>
+      <c r="E24" s="3">
         <v>363000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>584000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>432000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>315000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>333000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>449000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>371000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>253000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>108000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>262000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-389000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>248000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>335000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>172000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>282000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>160000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>116000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>96000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>342000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>345000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-178000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>152000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-38000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>639000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-44000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>306000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>153000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>298000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>413000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>693000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2399,210 +2447,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2249000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2157000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1713000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2006000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1725000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1625000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1560000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1535000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>175000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1743000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1473000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-933000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1359000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1481000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1468000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1395000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1338000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1126000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>771000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1473000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1088000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>813000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>215000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>185000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3820000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>492000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>731000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1011000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1228000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>761000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1490000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1355000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2141000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>2139000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2059000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1622000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1918000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1657000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1535000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1482000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1472000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>111000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1709000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1426000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-984000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1327000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1426000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1422000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1387000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1304000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1103000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>685000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1400000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1040000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>772000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>146000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>151000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3844000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>438000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>657000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>958000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1183000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>712000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1378000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1244000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2050000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2702,8 +2759,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2756,55 +2816,58 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-19000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>1000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-7000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-8000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>113000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>9000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-521000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>486000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>190000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>717000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>634000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-692000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2904,8 +2967,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3005,210 +3071,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-12000</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7000</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100000</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q32" s="3">
         <v>14000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-481000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-483000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-465000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-484000</v>
       </c>
       <c r="U32" s="3">
         <v>-484000</v>
       </c>
       <c r="V32" s="3">
+        <v>-484000</v>
+      </c>
+      <c r="W32" s="3">
         <v>-500000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-494000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-502000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-266000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-264000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-248000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-175000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-167000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-311000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-268000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-203000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-265000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-253000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-218000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2139000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2059000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1622000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1918000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1657000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1535000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1482000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1472000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>111000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1709000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1426000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-984000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1327000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1426000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1422000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1387000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1304000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1084000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>686000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1393000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1032000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>753000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>135000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>264000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3835000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-83000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1143000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1148000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1900000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1346000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>686000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1238000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2048000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3308,215 +3383,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2139000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2059000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1622000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1918000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1657000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1535000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1482000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1472000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>111000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1709000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1426000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-984000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1327000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1426000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1422000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1387000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1304000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1084000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>686000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1393000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1032000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>753000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>135000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>264000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3835000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-83000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1143000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1148000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1900000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1346000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>686000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1238000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2048000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3552,8 +3636,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3589,109 +3674,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8305000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6818000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7435000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5966000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4782000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5157000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5578000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6682000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6011000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5607000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6587000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5456000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5391000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5893000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6220000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5381000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4767000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6040000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7832000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7476000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8051000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8579000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8802000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10001000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6975000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8001000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4937000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7341000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6819000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6240000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6152000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13799000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>11068000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3791,412 +3880,427 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>32922000</v>
+      </c>
+      <c r="E43" s="3">
         <v>31015000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>31793000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>29441000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>28071000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26667000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>25546000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24781000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23833000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23384000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>22977000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22754000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>22873000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>22798000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>20642000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>21530000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>22230000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>20642000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>21022000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20437000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>19397000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>20275000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19185000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>19732000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>19439000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>17653000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>26729000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>17923000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>18029000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>17369000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>17757000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>16000000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>15246000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>14409000</v>
+      </c>
+      <c r="E44" s="3">
         <v>14153000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>13364000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>13806000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14012000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13618000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12768000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13465000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13047000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12386000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11777000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12050000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>11997000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>11327000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>10617000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>10443000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>10142000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>9749000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>9178000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>9426000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>9548000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>9498000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>9411000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>9843000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>10256000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>11506000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>9047000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>11242000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>10934000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>10474000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>10083000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>9068000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>8979000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8276000</v>
+      </c>
+      <c r="E45" s="3">
         <v>8023000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7740000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7905000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7792000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7474000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7241000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6836000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6334000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6646000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7076000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6258000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5654000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5486000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4964000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4467000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4323000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4309000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4018000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4653000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3883000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4200000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5978000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3935000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5604000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1715000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>35849000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1310000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1276000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1319000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1511000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1337000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1263000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>63912000</v>
+      </c>
+      <c r="E46" s="3">
         <v>60009000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>60332000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>57118000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>54657000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>52916000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>51133000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>51764000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>49225000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>48023000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>48417000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>46518000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>45915000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>45504000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>42443000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>41821000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>41462000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>40740000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>42050000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>41992000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>40879000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>42552000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>43376000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>43511000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>42274000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>38875000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>61577000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>37816000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>37058000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>35402000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>35503000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>40204000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>36556000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4239,267 +4343,276 @@
       <c r="P47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R47" s="3">
         <v>2603000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2618000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2675000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2766000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>14209000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2960000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13548000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13317000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13075000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12931000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3363000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4773000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7925000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4736000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4508000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3182000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3023000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3143000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2763000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18692000</v>
+      </c>
+      <c r="E48" s="3">
         <v>18615000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18755000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18224000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>18074000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>18034000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>17953000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17732000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17357000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17277000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17386000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17102000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17107000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16993000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16999000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>16470000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16607000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16748000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16930000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16393000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16565000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16655000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16842000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16757000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16907000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>15108000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11629000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14810000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15106000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>14824000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12297000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>10236000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>10115000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>83971000</v>
+      </c>
+      <c r="E49" s="3">
         <v>84758000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>85188000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>85571000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>86075000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>86161000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>86232000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>87918000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>87850000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>88604000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>89098000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>89748000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>90356000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>90381000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>90663000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>90214000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>91368000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>92434000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>92952000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>92631000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>93917000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>94264000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>94824000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>95088000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>95272000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>73081000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>61561000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>73727000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>74321000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>74672000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>74536000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>43380000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>43438000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4599,8 +4712,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4700,70 +4816,73 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5495000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5008000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4672000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5688000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6229000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5618000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5297000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5102000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4417000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3924000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4576000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6623000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6326000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6215000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6156000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7102000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6905000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6678000</v>
       </c>
-      <c r="U52" s="3" t="s">
+      <c r="V52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4796000</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>24</v>
@@ -4774,35 +4893,38 @@
       <c r="Z52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB52" s="3">
         <v>3701000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7735000</v>
       </c>
-      <c r="AC52" s="3" t="s">
+      <c r="AD52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7920000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7997000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9300000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8852000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>17976000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8697000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4902,109 +5024,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>173972000</v>
+      </c>
+      <c r="E54" s="3">
         <v>170431000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>171079000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>168672000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>167139000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>164864000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>162861000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>164822000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>161169000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>160187000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>161869000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>162443000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>162161000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>161636000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>158864000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>158225000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>159017000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>159366000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>161404000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>158772000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>158838000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>160608000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>162153000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>162399000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>161517000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>139572000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>139615000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>139009000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>138990000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>137380000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>134211000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>114939000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>101569000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5040,8 +5168,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5077,614 +5206,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16998000</v>
+      </c>
+      <c r="E57" s="3">
         <v>15979000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15895000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14552000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13433000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13444000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12897000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11834000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10939000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10522000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10698000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10315000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10128000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10060000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9896000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9017000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9732000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8270000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8751000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8667000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8043000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9182000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>8639000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8143000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7182000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10976000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7816000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10840000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11109000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10364000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11080000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10509000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9623000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5525000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4439000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4066000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>799000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3719000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3056000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2902000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3333000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1848000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>510000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1820000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2559000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2630000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1769000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1220000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2388000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>139000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>164000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>158000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>480000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1566000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1603000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>797000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1535000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1540000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3087000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5551000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6822000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7341000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4182000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4345000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1668000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1063000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23143000</v>
+      </c>
+      <c r="E59" s="3">
         <v>22251000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21880000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20453000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>19493000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19303000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19067000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18565000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17853000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17331000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17363000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15522000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15362000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15259000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27998000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>26968000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>27917000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>26623000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>26540000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>24984000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>25185000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>25574000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>26412000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>25884000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>26569000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17439000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>54190000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>17905000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>16972000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>16857000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>15943000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>14327000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>14382000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>63245000</v>
+      </c>
+      <c r="E60" s="3">
         <v>58579000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>58784000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53234000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>54332000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>52624000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>51499000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>52247000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>49565000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>45019000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>46761000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>45002000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>41760000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>40128000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>39114000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>38373000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>37788000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>35057000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>35449000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>34131000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>34794000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>36359000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>35848000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>35562000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>35291000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>31502000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>46594000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>35567000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>35422000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>31403000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>31368000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>26504000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>25068000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>33331000</v>
+      </c>
+      <c r="E61" s="3">
         <v>34496000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>35890000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>39910000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>39876000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>39890000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>40358000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>40415000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>41718000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>43744000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>43767000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>34224000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>34293000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>34341000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>30694000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31059000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>31274000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>31308000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>31327000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>30768000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>29916000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>29935000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>31026000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>31246000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>31210000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>43232000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>37701000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>37782000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>37910000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>41004000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>41192000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>38275000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>27246000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7296000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7307000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7200000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7154000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6646000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6946000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6942000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7071000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6941000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6967000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7511000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7514000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7442000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8106000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14842000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>17025000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>17927000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18979000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>19929000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>20904000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>21377000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>20972000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>21395000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>25481000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>26089000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>22808000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>28364000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>22734000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>22572000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>22918000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>20932000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>15785000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>15779000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5784,8 +5932,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5885,8 +6036,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5986,109 +6140,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>105828000</v>
+      </c>
+      <c r="E66" s="3">
         <v>102397000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>103941000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>102279000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>102892000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>101520000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>100903000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>101963000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100488000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>98050000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>100424000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>91197000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>88074000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>87251000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>86232000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>88038000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>88576000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>86904000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>88336000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>87464000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>87723000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>88898000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>89990000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>94020000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>94292000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>100161000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>97841000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>98541000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>98236000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>97642000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>95765000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>82833000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>70205000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6124,8 +6284,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6225,8 +6386,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6326,8 +6490,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6427,8 +6594,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6528,109 +6698,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>58020000</v>
+      </c>
+      <c r="E72" s="3">
         <v>57861000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>56718000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>56014000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>54104000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>54277000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>53589000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>52948000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>51488000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>53052000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>52154000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>51513000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>52489000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>52891000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>52269000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>51652000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>50271000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>50592000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>50265000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>50343000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>48954000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>49460000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>49423000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>50017000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>49744000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>60826000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>61594000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>61069000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>60548000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>59279000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>57823000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>57706000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>57027000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6730,8 +6906,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6831,8 +7010,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6932,109 +7114,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>66377000</v>
+      </c>
+      <c r="E76" s="3">
         <v>66280000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>65245000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>64514000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>62398000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>61516000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>60156000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>61114000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>58985000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>60485000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>59798000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>69596000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>72480000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>72795000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>72632000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>70187000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>70441000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>72462000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>73068000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>71308000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>71115000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>71710000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>72163000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>68379000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>67225000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>39411000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>41774000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>40468000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>40754000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>39738000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>38446000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>32106000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>31364000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7134,215 +7322,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2139000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2059000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1622000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1918000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1657000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1535000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1482000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1472000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>111000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1709000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1426000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-984000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1327000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1426000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1422000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1387000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1304000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1084000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>686000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1393000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1032000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>753000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>135000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>264000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3835000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-83000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1143000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1148000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1900000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1346000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>686000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1238000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2048000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7378,109 +7575,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>568000</v>
+      </c>
+      <c r="E83" s="3">
         <v>551000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>559000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>534000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>538000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>533000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>523000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>529000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>534000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>525000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>542000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>550000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>532000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>527000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1048000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1047000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>999000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1014000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1144000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1158000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1132000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1123000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1153000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1164000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>859000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>980000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>952000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>967000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>922000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>942000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>667000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>593000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>592000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7580,8 +7781,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7681,8 +7885,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7782,8 +7989,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7883,8 +8093,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7984,109 +8197,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3547000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1855000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4165000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4639000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>458000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1305000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1561000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2523000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2733000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>342000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4711000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3316000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>719000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-863000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4628000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>778000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1286000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>476000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3117000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1929000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1307000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>718000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1335000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1590000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>20000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>661000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2782000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2490000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2111000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1500000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2005000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1762000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2102000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8122,109 +8341,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-669000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-546000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-970000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-614000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-530000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-513000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1069000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-552000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-537000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-467000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-805000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-564000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-526000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-520000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1173000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-593000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-520000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-489000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1004000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-511000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-360000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-387000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-623000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-389000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-458000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-325000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-746000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-444000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-363000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-780000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-413000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-372000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8324,8 +8547,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8425,109 +8651,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-944000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-608000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-549000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>471000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-509000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-678000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-779000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-715000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-733000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>693000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-978000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-859000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-623000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-579000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-938000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-755000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-618000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-518000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1225000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-378000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-343000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>582000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-809000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>2096000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>3096000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1281000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-756000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-823000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-394000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-15954000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-781000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>738000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8563,109 +8795,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>983000</v>
+      </c>
+      <c r="E96" s="3">
         <v>915000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>914000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>910000</v>
       </c>
       <c r="G96" s="3">
         <v>910000</v>
       </c>
       <c r="H96" s="3">
+        <v>910000</v>
+      </c>
+      <c r="I96" s="3">
         <v>840000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>802000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>823000</v>
       </c>
       <c r="K96" s="3">
         <v>823000</v>
       </c>
       <c r="L96" s="3">
+        <v>823000</v>
+      </c>
+      <c r="M96" s="3">
         <v>769000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>767000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>838000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>844000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>790000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-791000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-794000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-798000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-745000</v>
       </c>
       <c r="U96" s="3">
         <v>-745000</v>
       </c>
       <c r="V96" s="3">
+        <v>-745000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-751000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-756000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-705000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-706000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-688000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-724000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-614000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-612000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-611000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-610000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-609000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-564000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-536000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-535000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8765,8 +9001,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8866,8 +9105,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8967,307 +9209,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1069000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1840000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2154000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3923000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-353000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1056000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1868000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1158000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1584000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2007000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2618000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2377000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-628000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1096000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2849000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>617000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1882000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1745000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1530000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2060000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1556000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1539000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1769000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-692000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4175000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1362000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1670000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1129000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-688000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2874000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>11050000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>699000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E101" s="3">
         <v>16000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-39000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>23000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>14000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-15000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>18000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>15000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-37000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-35000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>15000</v>
       </c>
       <c r="Q101" s="3">
         <v>15000</v>
       </c>
       <c r="R101" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S101" s="3">
         <v>-37000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-35000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>15000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-11000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-69000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>56000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>23000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>43000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>21000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>8000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-94000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>46000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-81000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-25000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>41000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-93000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-137000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1521000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-599000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1466000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1177000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-366000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-413000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1125000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>673000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>412000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-980000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1129000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>65000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-514000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-345000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>856000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>603000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1249000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1772000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>351000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-578000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-536000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-216000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1200000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3015000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1049000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>646000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>39000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>525000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>574000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>70000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-16832000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>11938000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3402000</v>
       </c>
     </row>
